--- a/assets/業務マトリクス一覧_テンプレート.xlsx
+++ b/assets/業務マトリクス一覧_テンプレート.xlsx
@@ -48,77 +48,74 @@
   <numFmts count="0"/>
   <fonts count="14">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Yu Gothic UI"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <color rgb="001F4E79"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <color rgb="00C55A11"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <color rgb="00A6A6A6"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <color rgb="000066CC"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="007030A0"/>
